--- a/grupos/1EV - Estadisticos 20241.xlsx
+++ b/grupos/1EV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -161,21 +161,21 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
@@ -194,40 +194,52 @@
     <t>AJACTLE</t>
   </si>
   <si>
+    <t>ABURTO</t>
+  </si>
+  <si>
     <t>CESMA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>XOCHICALE</t>
   </si>
   <si>
+    <t>CORDERO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>SANDRA GABRIELA</t>
   </si>
   <si>
+    <t>ERIC ELIU</t>
+  </si>
+  <si>
     <t>ARANZI</t>
   </si>
   <si>
-    <t>EMERSON IVAN</t>
-  </si>
-  <si>
     <t>JESUS FABIAN</t>
+  </si>
+  <si>
+    <t>SABDIEL JIREH</t>
   </si>
   <si>
     <t>LEONEL</t>
@@ -776,28 +788,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -824,10 +836,10 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>6</v>
@@ -836,13 +848,13 @@
         <v>5</v>
       </c>
       <c r="AD4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -877,28 +889,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -925,7 +937,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -978,28 +990,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1029,10 +1041,10 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1041,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1079,28 +1091,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1127,13 +1139,13 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1145,7 +1157,7 @@
         <v>9</v>
       </c>
       <c r="AF7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1180,28 +1192,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1231,10 +1243,10 @@
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1243,10 +1255,10 @@
         <v>8</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1281,28 +1293,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1329,25 +1341,25 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>8</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1382,28 +1394,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1436,7 +1448,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1448,7 +1460,7 @@
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1483,28 +1495,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1531,13 +1543,13 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1549,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="AF11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1584,28 +1596,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1650,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1685,28 +1697,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1733,19 +1745,19 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>5</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13">
         <v>10</v>
@@ -1786,28 +1798,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1834,7 +1846,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1852,7 +1864,7 @@
         <v>9</v>
       </c>
       <c r="AF14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1887,28 +1899,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1938,7 +1950,7 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -1988,28 +2000,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2042,13 +2054,13 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>8</v>
       </c>
       <c r="AD16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE16">
         <v>10</v>
@@ -2089,28 +2101,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2137,25 +2149,25 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>6</v>
       </c>
       <c r="AD17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2190,28 +2202,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2238,10 +2250,10 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2253,10 +2265,10 @@
         <v>8</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2291,28 +2303,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2345,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2392,28 +2404,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2446,19 +2458,19 @@
         <v>9</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>6</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE20">
         <v>9</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2493,28 +2505,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2541,25 +2553,25 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>7</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE21">
         <v>9</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2594,28 +2606,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2829,43 +2841,43 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
+        <v>95.5</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>95.2</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>95</v>
       </c>
-      <c r="M4">
-        <v>100</v>
-      </c>
-      <c r="N4">
-        <v>90</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
-        <v>100</v>
-      </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
-        <v>90</v>
-      </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W4">
         <v>100</v>
@@ -2912,7 +2924,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -2936,7 +2948,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -2983,13 +2995,13 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -2998,7 +3010,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3007,13 +3019,13 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3022,7 +3034,7 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -3143,7 +3155,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M8">
         <v>93.8</v>
@@ -3167,7 +3179,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U8">
         <v>93.8</v>
@@ -3297,7 +3309,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3321,7 +3333,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -3374,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3398,7 +3410,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -3451,7 +3463,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -3475,7 +3487,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -3528,7 +3540,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -3537,7 +3549,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3552,7 +3564,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -3561,7 +3573,7 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -3605,13 +3617,13 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3629,13 +3641,13 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W14">
         <v>100</v>
@@ -3682,16 +3694,16 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3706,16 +3718,16 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="X15">
         <v>100</v>
@@ -3759,7 +3771,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -3783,7 +3795,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -3836,7 +3848,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3860,7 +3872,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -3907,13 +3919,13 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="M18">
         <v>93.8</v>
@@ -3931,13 +3943,13 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="U18">
         <v>93.8</v>
@@ -3990,13 +4002,13 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M19">
         <v>87.5</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="O19">
         <v>93.8</v>
@@ -4014,13 +4026,13 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U19">
         <v>87.5</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="W19">
         <v>93.8</v>
@@ -4067,13 +4079,13 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>50</v>
+        <v>76.2</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -4091,13 +4103,13 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
-        <v>50</v>
+        <v>76.2</v>
       </c>
       <c r="W20">
         <v>100</v>
@@ -4144,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -4168,7 +4180,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -4215,13 +4227,13 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="M22">
         <v>93.8</v>
@@ -4230,7 +4242,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4239,13 +4251,13 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="U22">
         <v>93.8</v>
@@ -4254,7 +4266,7 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -4358,19 +4370,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4381,7 +4393,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -4390,19 +4402,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G4" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4413,7 +4425,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4434,7 +4446,7 @@
         <v>15.8</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4466,7 +4478,7 @@
         <v>10.5</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4477,7 +4489,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4486,19 +4498,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4509,7 +4521,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -4530,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4612,7 +4624,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4650,10 +4662,10 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4667,16 +4679,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920285</v>
+        <v>24330051920321</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4690,22 +4702,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920289</v>
+        <v>24330051920285</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4716,13 +4728,13 @@
         <v>24330051920290</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4736,24 +4748,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
+        <v>24330051920323</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>24330051920391</v>
       </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6">
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20241.xlsx
+++ b/grupos/1EV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -155,12 +155,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -173,7 +173,7 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Breniz Camarillo Lysette</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -191,15 +191,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ABURTO</t>
-  </si>
-  <si>
-    <t>CESMA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -209,15 +200,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>CORDERO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -225,15 +207,6 @@
   </si>
   <si>
     <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SANDRA GABRIELA</t>
-  </si>
-  <si>
-    <t>ERIC ELIU</t>
-  </si>
-  <si>
-    <t>ARANZI</t>
   </si>
   <si>
     <t>JESUS FABIAN</t>
@@ -797,7 +770,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>8</v>
@@ -845,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD4">
         <v>8</v>
@@ -898,7 +871,7 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>8</v>
@@ -946,7 +919,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD5">
         <v>8</v>
@@ -999,7 +972,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>6</v>
@@ -1100,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>9</v>
@@ -1201,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>7</v>
@@ -1249,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>8</v>
@@ -1302,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>6</v>
@@ -1403,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>10</v>
@@ -1451,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD10">
         <v>10</v>
@@ -1504,7 +1477,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>7</v>
@@ -1552,7 +1525,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD11">
         <v>8</v>
@@ -1605,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>10</v>
@@ -1706,7 +1679,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>9</v>
@@ -1807,7 +1780,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>8</v>
@@ -1908,7 +1881,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -2009,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>10</v>
@@ -2057,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD16">
         <v>10</v>
@@ -2110,7 +2083,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>8</v>
@@ -2211,7 +2184,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>8</v>
@@ -2259,7 +2232,7 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>8</v>
@@ -2312,7 +2285,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -2413,7 +2386,7 @@
         <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>7</v>
@@ -2461,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD20">
         <v>9</v>
@@ -2514,7 +2487,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>8</v>
@@ -2615,7 +2588,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2927,7 +2900,7 @@
         <v>95.5</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>56.3</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -2951,7 +2924,7 @@
         <v>95.5</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>56.3</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3158,7 +3131,7 @@
         <v>93.2</v>
       </c>
       <c r="M8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3182,7 +3155,7 @@
         <v>93.2</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3928,7 +3901,7 @@
         <v>93.2</v>
       </c>
       <c r="M18">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -3952,7 +3925,7 @@
         <v>93.2</v>
       </c>
       <c r="U18">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4005,7 +3978,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="M19">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="N19">
         <v>95.2</v>
@@ -4029,7 +4002,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="U19">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V19">
         <v>95.2</v>
@@ -4236,7 +4209,7 @@
         <v>93.2</v>
       </c>
       <c r="M22">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4260,7 +4233,7 @@
         <v>93.2</v>
       </c>
       <c r="U22">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4329,7 +4302,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -4338,19 +4311,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>63.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>36.8</v>
+        <v>21.1</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4361,7 +4334,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -4382,7 +4355,7 @@
         <v>21.1</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4624,7 +4597,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4656,22 +4629,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920282</v>
+        <v>24330051920290</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4679,19 +4652,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920321</v>
+        <v>24330051920323</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -4702,93 +4675,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920285</v>
+        <v>24330051920391</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920290</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920323</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920391</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20241.xlsx
+++ b/grupos/1EV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -191,6 +191,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -200,13 +206,22 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ALEYDA MONSERRAT</t>
   </si>
   <si>
     <t>JESUS FABIAN</t>
@@ -4158,7 +4173,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4190,22 +4205,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920290</v>
+        <v>24330051920283</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4213,22 +4228,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920323</v>
+        <v>24330051920283</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4236,24 +4251,208 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920391</v>
+        <v>24330051920283</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
         <v>62</v>
       </c>
       <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920283</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920312</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920312</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920312</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920312</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920290</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920323</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
         <v>65</v>
       </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920391</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="G4">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20241.xlsx
+++ b/grupos/1EV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -158,24 +158,24 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -194,43 +194,52 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>RUL</t>
+  </si>
+  <si>
+    <t>XOCHICALE</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
+    <t>JOSE GABRIEL</t>
+  </si>
+  <si>
+    <t>SANDRA GABRIELA</t>
+  </si>
+  <si>
+    <t>SABDIEL JIREH</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
     <t>ALEYDA MONSERRAT</t>
-  </si>
-  <si>
-    <t>JESUS FABIAN</t>
-  </si>
-  <si>
-    <t>SABDIEL JIREH</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
   </si>
 </sst>
 </file>
@@ -781,16 +790,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -802,13 +811,13 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -870,16 +879,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -897,10 +906,10 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -959,16 +968,16 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -980,16 +989,16 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1048,16 +1057,16 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1069,10 +1078,10 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1137,16 +1146,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1158,13 +1167,13 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>8</v>
@@ -1226,16 +1235,16 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1315,16 +1324,16 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1404,16 +1413,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1425,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1493,16 +1502,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1582,16 +1591,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1603,13 +1612,13 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>9</v>
@@ -1671,16 +1680,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1760,16 +1769,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1781,16 +1790,16 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>6</v>
@@ -1849,16 +1858,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1938,16 +1947,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -1959,13 +1968,13 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>7</v>
@@ -2027,16 +2036,16 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2048,7 +2057,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2116,16 +2125,16 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2137,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2205,16 +2214,16 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2226,16 +2235,16 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>9</v>
@@ -2294,16 +2303,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2321,10 +2330,10 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>9</v>
@@ -2383,16 +2392,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2407,13 +2416,13 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2597,13 +2606,13 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -2665,10 +2674,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S5">
-        <v>56.3</v>
+        <v>70.8</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -2733,7 +2742,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2869,10 +2878,10 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S8">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -3005,7 +3014,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3073,7 +3082,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3141,7 +3150,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3209,7 +3218,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3277,13 +3286,13 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -3345,13 +3354,13 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U15">
         <v>87.5</v>
@@ -3413,7 +3422,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3481,7 +3490,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3549,10 +3558,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S18">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -3617,13 +3626,13 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S19">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T19">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="U19">
         <v>93.8</v>
@@ -3649,7 +3658,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -3670,7 +3679,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -3685,13 +3694,13 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -3753,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3821,10 +3830,10 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S22">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -3922,7 +3931,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -3931,19 +3940,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G3" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3954,7 +3963,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3963,19 +3972,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="G4" s="2">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3986,7 +3995,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -3995,19 +4004,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4027,19 +4036,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4050,7 +4059,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4082,7 +4091,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -4103,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4173,7 +4182,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4211,16 +4220,16 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4234,16 +4243,16 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4251,22 +4260,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920283</v>
+        <v>24330051920293</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4274,16 +4283,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920283</v>
+        <v>24330051920293</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -4297,22 +4306,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920312</v>
+        <v>24330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4320,22 +4329,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920312</v>
+        <v>24330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4343,22 +4352,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920312</v>
+        <v>24330051920391</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4369,13 +4378,13 @@
         <v>23330051920312</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -4384,75 +4393,6 @@
         <v>45</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920290</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920323</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920391</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20241.xlsx
+++ b/grupos/1EV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -161,6 +161,9 @@
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
@@ -170,9 +173,6 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -191,49 +191,40 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>AJACTLE</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>RUL</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>RUL</t>
-  </si>
-  <si>
     <t>XOCHICALE</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>JOSE GABRIEL</t>
+  </si>
+  <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
-    <t>JOSE GABRIEL</t>
-  </si>
-  <si>
     <t>SANDRA GABRIELA</t>
-  </si>
-  <si>
-    <t>SABDIEL JIREH</t>
   </si>
   <si>
     <t>LEONEL</t>
@@ -802,10 +793,10 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -891,10 +882,10 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -912,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -980,10 +971,10 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1001,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1069,10 +1060,10 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1093,7 +1084,7 @@
         <v>9</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1158,10 +1149,10 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1179,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1247,10 +1238,10 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1271,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1336,10 +1327,10 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1360,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1425,10 +1416,10 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1514,10 +1505,10 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1603,10 +1594,10 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1624,7 +1615,7 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>9</v>
@@ -1692,10 +1683,10 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1781,10 +1772,10 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1802,7 +1793,7 @@
         <v>6</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1870,10 +1861,10 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1959,10 +1950,10 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -1980,10 +1971,10 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2048,10 +2039,10 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2072,7 +2063,7 @@
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2137,10 +2128,10 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2158,7 +2149,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2226,10 +2217,10 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2250,7 +2241,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2315,10 +2306,10 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2336,10 +2327,10 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2404,10 +2395,10 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2751,7 +2742,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3227,7 +3218,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -3363,7 +3354,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U15">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -3635,7 +3626,7 @@
         <v>96.8</v>
       </c>
       <c r="U19">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -3839,7 +3830,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -3908,19 +3899,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G2" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3963,7 +3954,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3984,7 +3975,7 @@
         <v>5.3</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3995,7 +3986,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4004,19 +3995,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4027,7 +4018,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4048,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4059,7 +4050,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4080,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4214,16 +4205,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920283</v>
+        <v>24330051920293</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4237,22 +4228,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920283</v>
+        <v>24330051920293</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4263,19 +4254,19 @@
         <v>24330051920293</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4283,22 +4274,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920293</v>
+        <v>24330051920283</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4306,22 +4297,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920282</v>
+        <v>24330051920283</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4329,22 +4320,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920323</v>
+        <v>24330051920282</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4355,13 +4346,13 @@
         <v>24330051920391</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4378,13 +4369,13 @@
         <v>23330051920312</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>

--- a/grupos/1EV - Estadisticos 20241.xlsx
+++ b/grupos/1EV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="69">
   <si>
     <t>Materia</t>
   </si>
@@ -158,15 +158,15 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Breniz Camarillo Lysette</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -200,9 +200,6 @@
     <t>AJACTLE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -225,9 +222,6 @@
   </si>
   <si>
     <t>SANDRA GABRIELA</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
   </si>
   <si>
     <t>ALEYDA MONSERRAT</t>
@@ -778,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -799,7 +793,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -867,7 +861,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -956,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>7</v>
@@ -977,7 +971,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1045,7 +1039,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1134,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1223,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1312,7 +1306,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1333,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1401,7 +1395,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1490,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1579,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1668,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1757,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>6</v>
@@ -1846,7 +1840,7 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>8</v>
@@ -1867,7 +1861,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1935,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1956,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2024,7 +2018,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -2045,7 +2039,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2113,7 +2107,7 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -2202,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>8</v>
@@ -2223,7 +2217,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2291,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>7</v>
@@ -2380,7 +2374,7 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>6</v>
@@ -2401,7 +2395,7 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2591,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -2727,7 +2721,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3339,7 +3333,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3543,7 +3537,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3815,7 +3809,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -3922,7 +3916,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -3931,19 +3925,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="G3" s="2">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3954,7 +3948,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3975,7 +3969,7 @@
         <v>5.3</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3986,7 +3980,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4173,7 +4167,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4211,16 +4205,16 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4234,16 +4228,16 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4257,10 +4251,10 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -4280,16 +4274,16 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4297,10 +4291,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920283</v>
+        <v>24330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
         <v>63</v>
@@ -4309,10 +4303,10 @@
         <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4320,10 +4314,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920282</v>
+        <v>23330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
@@ -4332,58 +4326,12 @@
         <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920391</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920312</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
